--- a/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
@@ -526,10 +526,10 @@
         <v>39</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>38</v>
@@ -538,7 +538,7 @@
         <v>97.44</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -549,7 +549,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -558,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5">
         <v>8.6</v>
@@ -666,7 +666,7 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -683,13 +683,13 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -800,10 +800,10 @@
         <v>39</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>38</v>
@@ -812,7 +812,7 @@
         <v>97.44</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -823,7 +823,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -832,10 +832,10 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5">
         <v>8.6</v>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
@@ -617,16 +617,19 @@
         <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>32</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -640,16 +643,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.56</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -663,16 +669,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.44</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -760,7 +769,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -777,16 +786,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>97.56</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -812,7 +821,7 @@
         <v>97.44</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
@@ -695,16 +695,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.31999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -838,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>87.09999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>LORENA</t>
   </si>
 </sst>
 </file>
@@ -860,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -890,6 +899,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920234</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,15 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LORENA</t>
   </si>
 </sst>
 </file>
@@ -781,7 +772,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -807,7 +798,7 @@
         <v>97.56</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -833,7 +824,7 @@
         <v>97.44</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -859,7 +850,7 @@
         <v>90.31999999999999</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -899,29 +890,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920234</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
